--- a/extenbooks/XS1501.xlsx
+++ b/extenbooks/XS1501.xlsx
@@ -447,22 +447,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B44"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="56" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>XS1501 — Working Class Unproductive Labor (Mohun 2013)</t>
+          <t>XS1501 — Unproductive Working-Class Employment Share (Mohun 2014)</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Mohun 2013 RRPE, units=thousands_workers</t>
+          <t>Mohun 2014, RRPE 46(3):355-379, units=share</t>
         </is>
       </c>
     </row>
@@ -480,338 +480,18 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1948</v>
+        <v>1964</v>
       </c>
       <c r="B3" s="3" t="n">
-        <v>6426.474620491641</v>
+        <v>0.251</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1949</v>
+        <v>2007</v>
       </c>
       <c r="B4" s="3" t="n">
-        <v>7106.109482528167</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>1950</v>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>7483.248699239114</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>1951</v>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>8103.83283219278</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>1952</v>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>8220.910671663627</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>1953</v>
-      </c>
-      <c r="B8" s="3" t="n">
-        <v>8510.931198120761</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>1954</v>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>8584.46848106546</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>1955</v>
-      </c>
-      <c r="B10" s="3" t="n">
-        <v>8733.495218965976</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>1956</v>
-      </c>
-      <c r="B11" s="3" t="n">
-        <v>9026.6250735293</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>1957</v>
-      </c>
-      <c r="B12" s="3" t="n">
-        <v>9813.301272711682</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>1958</v>
-      </c>
-      <c r="B13" s="3" t="n">
-        <v>10566.31007668152</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>1959</v>
-      </c>
-      <c r="B14" s="3" t="n">
-        <v>11052.22536935331</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>1960</v>
-      </c>
-      <c r="B15" s="3" t="n">
-        <v>11923.43468469107</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>1961</v>
-      </c>
-      <c r="B16" s="3" t="n">
-        <v>12305.37608076324</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>1962</v>
-      </c>
-      <c r="B17" s="3" t="n">
-        <v>12472.65862437039</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>1963</v>
-      </c>
-      <c r="B18" s="3" t="n">
-        <v>12809.82281487248</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>1964</v>
-      </c>
-      <c r="B19" s="3" t="n">
-        <v>12724.58770688313</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>1965</v>
-      </c>
-      <c r="B20" s="3" t="n">
-        <v>12733.75395994997</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>1966</v>
-      </c>
-      <c r="B21" s="3" t="n">
-        <v>13206.1379726572</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>1967</v>
-      </c>
-      <c r="B22" s="3" t="n">
-        <v>13906.73139937009</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>1968</v>
-      </c>
-      <c r="B23" s="3" t="n">
-        <v>14775.02345010496</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1969</v>
-      </c>
-      <c r="B24" s="3" t="n">
-        <v>15778.83892030412</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>1970</v>
-      </c>
-      <c r="B25" s="3" t="n">
-        <v>16279.75171418903</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>1971</v>
-      </c>
-      <c r="B26" s="3" t="n">
-        <v>16499.41066427764</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>1972</v>
-      </c>
-      <c r="B27" s="3" t="n">
-        <v>17334.63034387472</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>1973</v>
-      </c>
-      <c r="B28" s="3" t="n">
-        <v>16928.83613301461</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>1974</v>
-      </c>
-      <c r="B29" s="3" t="n">
-        <v>16701.75804581029</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>1975</v>
-      </c>
-      <c r="B30" s="3" t="n">
-        <v>16882.23870338245</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>1976</v>
-      </c>
-      <c r="B31" s="3" t="n">
-        <v>17234.66986652348</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>1977</v>
-      </c>
-      <c r="B32" s="3" t="n">
-        <v>17886.56380248285</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>1978</v>
-      </c>
-      <c r="B33" s="3" t="n">
-        <v>18533.28974290524</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>1979</v>
-      </c>
-      <c r="B34" s="3" t="n">
-        <v>20420.689300579</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>1980</v>
-      </c>
-      <c r="B35" s="3" t="n">
-        <v>20721.72850438085</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>1981</v>
-      </c>
-      <c r="B36" s="3" t="n">
-        <v>21099.64981822276</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>1982</v>
-      </c>
-      <c r="B37" s="3" t="n">
-        <v>21191.77056470669</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>1983</v>
-      </c>
-      <c r="B38" s="3" t="n">
-        <v>21250.74035783025</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>1984</v>
-      </c>
-      <c r="B39" s="3" t="n">
-        <v>20950.70353425276</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>1985</v>
-      </c>
-      <c r="B40" s="3" t="n">
-        <v>21170.1507754911</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>1986</v>
-      </c>
-      <c r="B41" s="3" t="n">
-        <v>21610.57887021104</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>1987</v>
-      </c>
-      <c r="B42" s="3" t="n">
-        <v>22159.83787178462</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>1988</v>
-      </c>
-      <c r="B43" s="3" t="n">
-        <v>23566.49598549192</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>1989</v>
-      </c>
-      <c r="B44" s="3" t="n">
-        <v>24673.94837387865</v>
+        <v>0.3</v>
       </c>
     </row>
   </sheetData>
@@ -825,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B39"/>
+  <dimension ref="A1:B47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -864,7 +544,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Working Class Unproductive Labor (Mohun 2013)</t>
+          <t>Unproductive Working-Class Employment Share (Mohun 2014)</t>
         </is>
       </c>
     </row>
@@ -896,7 +576,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>thousands_workers</t>
+          <t>share</t>
         </is>
       </c>
     </row>
@@ -920,7 +600,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1948-1989</t>
+          <t>1964-2010</t>
         </is>
       </c>
     </row>
@@ -997,7 +677,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Mohun 2013 RRPE</t>
+          <t>Mohun 2014, RRPE 46(3):355-379</t>
         </is>
       </c>
     </row>
@@ -1014,43 +694,55 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t># XS1501 — Working Class Unproductive Labor (Mohun 2013)</t>
+          <t>&gt; **D4 REBUILD (2026-07-02) — SUPERSEDES the text below (pending D5 doc-regen).**</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>&gt; This series has been rebuilt from Mohun's ACTUAL published estimates: unproductive working-class SHARE of total employment (Mohun 2013 Fig 2): 1964=25.1%, peak 2007=30.0%.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>**Status**: book_period_validated</t>
+          <t>&gt; Units are now a **share/ratio over 1964-2010** (benchmark anchors, table/text-grade), NOT</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>&gt; thousands of FTE over 1948-1989. The old 1948-1989 thousands series was a mislabeled</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>**Chapter**: External study — Mohun (2013). **Status**: book_period_validated. **Period**: 1948-1989. **Units**: thousands of workers.</t>
+          <t>&gt; ST2 decomposition (DIV-050/051) and is retained as a variant arm (chopped/_variants_ST2/).</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>&gt; Attribution: **Mohun (2014), RRPE 46(3):355-379**, DOI 10.1177/0486613413506080.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>## Definition</t>
+          <t>&gt; Source: `data/source/external_studies/mohun_2013_published_shares.csv`. See D4 report.</t>
         </is>
       </c>
     </row>
@@ -1062,7 +754,7 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Unproductive workers in the *working class* component of total unproductive labor (excluding managerial/supervisory). Mohun's 2013 RRPE paper decomposes total Lu into Working Class (Luw) and Managerial (Lum) categories.</t>
+          <t># XS1501 — Working Class Unproductive Labor (Mohun 2013)</t>
         </is>
       </c>
     </row>
@@ -1074,7 +766,7 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>## Source</t>
+          <t>**Status**: book_period_validated</t>
         </is>
       </c>
     </row>
@@ -1086,7 +778,7 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>`data/source/external_studies/Mohun_unproductive_decomposition_1948_1989.csv`, column `Luw_mohun`. 1948=6,426K; 1989=24,674K.</t>
+          <t>**Chapter**: External study — Mohun (2013). **Status**: book_period_validated. **Period**: 1948-1989. **Units**: thousands of workers.</t>
         </is>
       </c>
     </row>
@@ -1098,7 +790,7 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>## Citation</t>
+          <t>## Definition</t>
         </is>
       </c>
     </row>
@@ -1110,7 +802,7 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Mohun, Simon. 2013. 'Unproductive Labor in the U.S. Economy 1964-2010.' Review of Radical Political Economics 46(3): 355-379.</t>
+          <t>Unproductive workers in the *working class* component of total unproductive labor (excluding managerial/supervisory). Mohun's 2013 RRPE paper decomposes total Lu into Working Class (Luw) and Managerial (Lum) categories.</t>
         </is>
       </c>
     </row>
@@ -1122,7 +814,7 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>## Source</t>
         </is>
       </c>
     </row>
@@ -1133,6 +825,54 @@
     <row r="39">
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
+        <is>
+          <t>`data/source/external_studies/Mohun_unproductive_decomposition_1948_1989.csv`, column `Luw_mohun`. 1948=6,426K; 1989=24,674K.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>## Citation</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Mohun, Simon. 2013. 'Unproductive Labor in the U.S. Economy 1964-2010.' Review of Radical Political Economics 46(3): 355-379.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
         <is>
           <t>*Generated by anu-ingestion.*</t>
         </is>
@@ -1149,7 +889,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1182,12 +922,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Taking the economy as a whole, these growing "unproductive" expenditures eat into the surplus-value produced and tend to effect a decline in the rate of the net surplus-value realized. It is these net results which guide capitalists in their business decisions and which determine the trends of capitalist development.... (Gillman 1957: 85)</t>
+          <t>STUDY ANCHOR (Decision 0007 / T1, added 2026-07-01 review): Mohun 2013 publishes the unproductive working class ONLY as SHARES (Figure 2), never as a year-by-year FTE-level table. Verbatim published anchors: unproductive working-class EMPLOYMENT share 1964 = 25.1% of total employment, peak 2007 = 30.0%; WAGE share 1964 = 18.6% of total wages, 1992 = 16.7%, 2010 = 18.1%. HONESTY NOTE: the shipped XS1501 series (source column Luw_mohun, 1948-1989) is NOT taken from any Mohun 2013 table; it is a separate ST-method (ST2) backward decomposition. Its 1964 unproductive-WC / total-employment ratio is 20.3%, which does NOT reproduce Mohun's published 25.1%. There is therefore no Mohun 2013 published level anchor; the registry 1948 reference value (6426.4746) is tautological (equals the source CSV = the final output).</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>KB: Technical/Knowledge_Base/external_papers/productive_labor/2013_Mohun_Unproductive_1964_2010/full_transcription.md</t>
+          <t>Mohun 2013, Figure 2 (Unproductive Working Class Shares of Total Employment and Total Wages), Section 4.1, RRPE 46(3):355-379</t>
         </is>
       </c>
     </row>
@@ -1199,12 +939,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Any laboring activity involved in these "metamorphoses" of capital (M – C and C' – M') adds no new value, and is unproductive. Only the wage-labor involved in the transformation of productive capital into commodity capital is productive.</t>
+          <t>Taking the economy as a whole, these growing "unproductive" expenditures eat into the surplus-value produced and tend to effect a decline in the rate of the net surplus-value realized. It is these net results which guide capitalists in their business decisions and which determine the trends of capitalist development.... (Gillman 1957: 85)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>KB: Technical/Knowledge_Base/external_papers/productive_labor/2013_Mohun_Unproductive_1964_2010/full_transcription.md</t>
+          <t>KB: Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/2013_Mohun_Unproductive_1964_2010/full_transcription.md</t>
         </is>
       </c>
     </row>
@@ -1216,12 +956,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Separating "pure" organization from authoritarian hierarchy and supervision is both theoretically doubtful and empirically impossible. The labor involved in such activities is conventionally treated as unproductive, and the same practice is followed here.</t>
+          <t>Any laboring activity involved in these "metamorphoses" of capital (M – C and C' – M') adds no new value, and is unproductive. Only the wage-labor involved in the transformation of productive capital into commodity capital is productive.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>KB: Technical/Knowledge_Base/external_papers/productive_labor/2013_Mohun_Unproductive_1964_2010/full_transcription.md</t>
+          <t>KB: Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/2013_Mohun_Unproductive_1964_2010/full_transcription.md</t>
         </is>
       </c>
     </row>
@@ -1233,12 +973,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Use the CES ratio of production workers to all workers for "Private industry"; for "Services" (1964-98); for "Logging"; for "Services" (1964-98) and for "Private service providing" (1998-2010).</t>
+          <t>Separating "pure" organization from authoritarian hierarchy and supervision is both theoretically doubtful and empirically impossible. The labor involved in such activities is conventionally treated as unproductive, and the same practice is followed here.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>KB: Technical/Knowledge_Base/external_papers/productive_labor/2013_Mohun_Unproductive_1964_2010/full_transcription.md</t>
+          <t>KB: Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/2013_Mohun_Unproductive_1964_2010/full_transcription.md</t>
         </is>
       </c>
     </row>
@@ -1250,12 +990,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>In this paper, "wages" means total compensation of employees (the sum of wage and salary accruals and employer-financed benefits). Where the meaning is restricted to accruals only, this is explicitly stated.</t>
+          <t>Use the CES ratio of production workers to all workers for "Private industry"; for "Services" (1964-98); for "Logging"; for "Services" (1964-98) and for "Private service providing" (1998-2010).</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>KB: Technical/Knowledge_Base/external_papers/productive_labor/2013_Mohun_Unproductive_1964_2010/full_transcription.md</t>
+          <t>KB: Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/2013_Mohun_Unproductive_1964_2010/full_transcription.md</t>
         </is>
       </c>
     </row>
@@ -1267,127 +1007,148 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Hence: The NIPA data for "Private Industries" must be adjusted to exclude "Farms" and "Private households."</t>
+          <t>In this paper, "wages" means total compensation of employees (the sum of wage and salary accruals and employer-financed benefits). Where the meaning is restricted to accruals only, this is explicitly stated.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>KB: Technical/Knowledge_Base/external_papers/productive_labor/2013_Mohun_Unproductive_1964_2010/full_transcription.md</t>
+          <t>KB: Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/2013_Mohun_Unproductive_1964_2010/full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>methodology_description</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Working class unproductive labor = unproductive workers who are members of the working class (i.e., whose work is controlled by others, who have no supervisory responsibilities above shop-floor level). Defined by location in the circuit of capital: these workers are involved in M→C or C'→M' transformations (purchasing inputs, selling outputs, financial, commercial, legal, business service activities) but are NOT supervisors. Identified via the BLS CES production worker / nonsupervisory worker criterion: the CES ratio of production workers to all workers is applied to NIPA full-time equivalents by sector, yielding working class employment. Unproductive working class = working class total minus productive working class.</t>
+          <t>Hence: The NIPA data for "Private Industries" must be adjusted to exclude "Farms" and "Private households."</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Mohun_2013, Section 3 and Appendix; full_transcription.md</t>
+          <t>KB: Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/2013_Mohun_Unproductive_1964_2010/full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>empirical_values</t>
+          <t>methodology_description</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Unproductive working class employment share of total employment: 1964 = 25.1%; peak 2007 = 30.0%; 2010 = ~29%. Trend: increased by about a fifth over 47 years. Unproductive working class wage share of total wages: 1964 = 18.6%; fell to 16.7% by 1992; rose back to 18.1% by 2010. Key finding: unlike total unproductive employment (which rose), the unproductive working class WAGE share is approximately flat and considerably lower than the employment share — a completely different pattern from supervisory wages.</t>
+          <t>Working class unproductive labor = unproductive workers who are members of the working class (i.e., whose work is controlled by others, who have no supervisory responsibilities above shop-floor level). Defined by location in the circuit of capital: these workers are involved in M→C or C'→M' transformations (purchasing inputs, selling outputs, financial, commercial, legal, business service activities) but are NOT supervisors. Identified via the BLS CES production worker / nonsupervisory worker criterion: the CES ratio of production workers to all workers is applied to NIPA full-time equivalents by sector, yielding working class employment. Unproductive working class = working class total minus productive working class.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Mohun_2013, Section 4.1, Fig 2; full_transcription.md</t>
+          <t>Mohun_2013, Section 3 and Appendix; full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>burden_finding</t>
+          <t>empirical_values</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Critical empirical finding: the unproductive working class absorbed 12.9% of money value added in 1964 and still 12.9% in 2010. Mean = 12.8%, standard deviation = 0.34 percentage points. Mohun concludes: 'Hence the burden to accumulation posed by the unproductive working class did not change over the whole period of 46 years.' This directly contradicts the received view (Moseley 1991, Paitaridis and Tsoulfidis 2012) that rising unproductive labor constitutes a growing burden on accumulation.</t>
+          <t>Unproductive working class employment share of total employment: 1964 = 25.1%; peak 2007 = 30.0%; 2010 = ~29%. Trend: increased by about a fifth over 47 years. Unproductive working class wage share of total wages: 1964 = 18.6%; fell to 16.7% by 1992; rose back to 18.1% by 2010. Key finding: unlike total unproductive employment (which rose), the unproductive working class WAGE share is approximately flat and considerably lower than the employment share — a completely different pattern from supervisory wages.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Mohun_2013, Section 5, Fig 4; full_transcription.md</t>
+          <t>Mohun_2013, Section 4.1, Fig 2; full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>class_composition</t>
+          <t>burden_finding</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Working class = ~81.3% of employed population (average 1964-2010, standard deviation 0.88). Supervisors (managers-plus-capitalists) = ~18.7% of employed population. Class proportions remained remarkably stable over the 47-year period. The working class is divided into productive and unproductive components by location in the circuit of capital. Unproductive working class employment = ~25.1-30% of total employment; productive working class = ~52-58% of total employment.</t>
+          <t>Critical empirical finding: the unproductive working class absorbed 12.9% of money value added in 1964 and still 12.9% in 2010. Mean = 12.8%, standard deviation = 0.34 percentage points. Mohun concludes: 'Hence the burden to accumulation posed by the unproductive working class did not change over the whole period of 46 years.' This directly contradicts the received view (Moseley 1991, Paitaridis and Tsoulfidis 2012) that rising unproductive labor constitutes a growing burden on accumulation.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Mohun_2013, Section 3; full_transcription.md</t>
+          <t>Mohun_2013, Section 5, Fig 4; full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>construction_note</t>
+          <t>class_composition</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Series registry construction: step 1 op=derive, formula='Lu × 0.813', inputs=['Mohun Lu'], output='XS1501-COMBINED'. This reflects the stable 81.3% working class share of total unproductive employment. Units: thousands of full-time equivalent employees. Period 1964-2010.</t>
+          <t>Working class = ~81.3% of employed population (average 1964-2010, standard deviation 0.88). Supervisors (managers-plus-capitalists) = ~18.7% of employed population. Class proportions remained remarkably stable over the 47-year period. The working class is divided into productive and unproductive components by location in the circuit of capital. Unproductive working class employment = ~25.1-30% of total employment; productive working class = ~52-58% of total employment.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Series registry XS1501; Mohun_2013, Section 3</t>
+          <t>Mohun_2013, Section 3; full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>construction_note</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>D4 REBUILD (2026-07-02): XS1501 rebuilt from Mohun's ACTUAL published estimates. Series is now Mohun's unproductive working-class share of total employment over 1964-2010, sourced from mohun_2013_published_shares.csv (Figure 2 (p.10/364)). Benchmark values (table/text-grade): 1964=0.251, 2007=0.300 (share of total employment). SUPERSEDES the fabricated registry formula 'Lu x 0.813'/'Lu x 0.187' (0.813/0.187 are Mohun's working-class/supervisor shares of TOTAL EMPLOYMENT, Section 3, never a split of Lu and never executed). The prior 1948-1989 thousands-FTE series was a mislabeled ST2 decomposition (DIV-050), retained as a variant arm (chopped/_variants_ST2/). Annual (non-benchmark) coverage is figure-grade -&gt; deferred to G2 (D4_G2_ACQUISITION_SPEC.md).</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Mohun 2013 (RRPE 46(3), pub 2014), Figure 2 (p.10/364); D4 rebuild</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>data_sources</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Primary data: BLS CES (Current Employment Statistics, both NAICS-based 1998-2010 and discontinued SIC-based 1964-1997); NIPA (BEA). Construction follows Shaikh and Tonak (1994) as revised by Mohun (2005). Working class employment: CES production worker ratio applied to NIPA ftes. Supervisory employment and wages: computed by subtraction (NIPA totals minus working class totals), which allocates all wages missing from CES — including stock options, bonuses, retroactive pay — to supervisory workers.</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Mohun_2013, Appendix; full_transcription.md</t>
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>methodology_summary</t>
+          <t>empirical_values</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Unproductive working-class employment (Lu_wc), 1964-2010. Derived as Mohun total unproductive Lu × 0.813 (stable working class share). Employment share rises from 25.1% (1964) to 30.0% (2007). Value-added absorption share flat at 12.8% throughout — no burden increase. Units: thousands of FTEs.</t>
+          <t>D4 rebuild anchors (XS1501): 1964=0.251, 2007=0.300 (share of total employment). Source = Mohun 2013 Figure 2 (p.10/364), text-reported benchmark values (table/text-grade). These are the primary validation reference values (external, non-tautological). Non-benchmark annual points are figure-grade and were NOT fabricated.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Mohun 2013 (RRPE 46(3), pub 2014), Figure 2 (p.10/364)</t>
         </is>
       </c>
     </row>
@@ -1395,23 +1156,20 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>methodology_summary</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Unproductive working-class employment (Lu_wc), 1964-2010. Derived as Mohun total unproductive Lu × 0.813 (stable working class share). Employment share rises from 25.1% (1964) to 30.0% (2007). Value-added absorption share flat at 12.8% throughout — no burden increase. Units: thousands of FTEs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>known_issues:</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>CORRECTION (2026-06-11 reconciliation): the registry construction op 'Lu x 0.813' is FABRICATED. The actual data is the Luw_mohun (working-class) column of Mohun's unproductive-employment decomposition (a ~0.456/0.544 split of Lu), NOT the 0.813 economy-wide working-class population share. Data verified correct against source; the registry construction formula must be corrected to a load of Luw_mohun.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>CES production worker criterion has coverage issues in Mining, Manufacturing, and Construction — 'supervisory workers' in these sectors include some non-supervisors, understating working class totals</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1177,7 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BLS proposed discontinuing production/non-supervisory series in 2004 (Federal Register 2005), citing classification difficulties; series was retained, but respondent difficulty may affect trend reliability</t>
+          <t>CORRECTION (2026-06-11 reconciliation): the registry construction op 'Lu x 0.813' is FABRICATED. The actual data is the Luw_mohun (working-class) column of Mohun's unproductive-employment decomposition (a ~0.456/0.544 split of Lu), NOT the 0.813 economy-wide working-class population share. Data verified correct against source; the registry construction formula must be corrected to a load of Luw_mohun.</t>
         </is>
       </c>
     </row>
@@ -1427,31 +1185,31 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
+          <t>CES production worker criterion has coverage issues in Mining, Manufacturing, and Construction — 'supervisory workers' in these sectors include some non-supervisors, understating working class totals</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>BLS proposed discontinuing production/non-supervisory series in 2004 (Federal Register 2005), citing classification difficulties; series was retained, but respondent difficulty may affect trend reliability</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
           <t>SIC-to-NAICS transition at 1998 handled by separate tables (Table 2 for SIC, Table 3 for NAICS)</t>
         </is>
       </c>
     </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>cross_references:</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>XS1502</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>XS1503</t>
         </is>
       </c>
     </row>
@@ -1459,49 +1217,65 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
+          <t>XS1502</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>XS1503</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
           <t>XS1504</t>
         </is>
       </c>
     </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>citations:</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Mohun_2013</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Mohun, Simon. 2013 [pub. 2014]. 'Unproductive Labor in the U.S. Economy 1964-2010.' Review of Radical Political Economics 46(3): 355-379. DOI: 10.1177/0486613413506080.</t>
-        </is>
-      </c>
-    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Mohun_2005</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Mohun, Simon. 2005. 'On measuring the wealth of nations: the US economy, 1964-2001.' Cambridge Journal of Economics 29(5): 799-815. DOI: 10.1093/cje/bei043.</t>
+          <t>citations:</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>Mohun_2013</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Mohun, Simon. 2013 [pub. 2014]. 'Unproductive Labor in the U.S. Economy 1964-2010.' Review of Radical Political Economics 46(3): 355-379. DOI: 10.1177/0486613413506080.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Mohun_2005</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Mohun, Simon. 2005. 'On measuring the wealth of nations: the US economy, 1964-2001.' Cambridge Journal of Economics 29(5): 799-815. DOI: 10.1093/cje/bei043.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>ST_1994</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. Measuring the Wealth of Nations: The Political Economy of National Accounts. Cambridge University Press.</t>
         </is>
@@ -1524,7 +1298,7 @@
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -1561,24 +1335,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>derive</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Mohun Lu</t>
-        </is>
-      </c>
+          <t>load</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>XS1501-COMBINED</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Lu — 0.813</t>
-        </is>
-      </c>
+          <t>XS1501-A</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3"/>
     <row r="4">
@@ -1610,7 +1376,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{"1948": 6426.4746}</t>
+          <t>{"1964": 0.251, "2007": 0.3}</t>
         </is>
       </c>
     </row>
@@ -1622,7 +1388,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[10000, 100000]</t>
+          <t>[0.2, 0.35]</t>
         </is>
       </c>
     </row>
@@ -1634,7 +1400,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>level_series</t>
+          <t>share_series</t>
         </is>
       </c>
     </row>
@@ -1646,7 +1412,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>level_series</t>
+          <t>share_series</t>
         </is>
       </c>
     </row>

--- a/extenbooks/XS1501.xlsx
+++ b/extenbooks/XS1501.xlsx
@@ -726,7 +726,7 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>&gt; ST2 decomposition (DIV-050/051) and is retained as a variant arm (chopped/_variants_ST2/).</t>
+          <t>&gt; predecessor-build decomposition (DIV-050/051) and is retained as a variant arm (chopped/_variants_predecessor-build/).</t>
         </is>
       </c>
     </row>
@@ -922,7 +922,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>STUDY ANCHOR (Decision 0007 / T1, added 2026-07-01 review): Mohun 2013 publishes the unproductive working class ONLY as SHARES (Figure 2), never as a year-by-year FTE-level table. Verbatim published anchors: unproductive working-class EMPLOYMENT share 1964 = 25.1% of total employment, peak 2007 = 30.0%; WAGE share 1964 = 18.6% of total wages, 1992 = 16.7%, 2010 = 18.1%. HONESTY NOTE: the shipped XS1501 series (source column Luw_mohun, 1948-1989) is NOT taken from any Mohun 2013 table; it is a separate ST-method (ST2) backward decomposition. Its 1964 unproductive-WC / total-employment ratio is 20.3%, which does NOT reproduce Mohun's published 25.1%. There is therefore no Mohun 2013 published level anchor; the registry 1948 reference value (6426.4746) is tautological (equals the source CSV = the final output).</t>
+          <t>STUDY ANCHOR (Decision 0007 / T1, added 2026-07-01 review): Mohun 2013 publishes the unproductive working class ONLY as SHARES (Figure 2), never as a year-by-year FTE-level table. Verbatim published anchors: unproductive working-class EMPLOYMENT share 1964 = 25.1% of total employment, peak 2007 = 30.0%; WAGE share 1964 = 18.6% of total wages, 1992 = 16.7%, 2010 = 18.1%. HONESTY NOTE: the shipped XS1501 series (source column Luw_mohun, 1948-1989) is NOT taken from any Mohun 2013 table; it is a separate ST-method (predecessor-build) backward decomposition. Its 1964 unproductive-WC / total-employment ratio is 20.3%, which does NOT reproduce Mohun's published 25.1%. There is therefore no Mohun 2013 published level anchor; the registry 1948 reference value (6426.4746) is tautological (equals the source CSV = the final output).</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>D4 REBUILD (2026-07-02): XS1501 rebuilt from Mohun's ACTUAL published estimates. Series is now Mohun's unproductive working-class share of total employment over 1964-2010, sourced from mohun_2013_published_shares.csv (Figure 2 (p.10/364)). Benchmark values (table/text-grade): 1964=0.251, 2007=0.300 (share of total employment). SUPERSEDES the fabricated registry formula 'Lu x 0.813'/'Lu x 0.187' (0.813/0.187 are Mohun's working-class/supervisor shares of TOTAL EMPLOYMENT, Section 3, never a split of Lu and never executed). The prior 1948-1989 thousands-FTE series was a mislabeled ST2 decomposition (DIV-050), retained as a variant arm (chopped/_variants_ST2/). Annual (non-benchmark) coverage is figure-grade -&gt; deferred to G2 (D4_G2_ACQUISITION_SPEC.md).</t>
+          <t>D4 REBUILD (2026-07-02): XS1501 rebuilt from Mohun's ACTUAL published estimates. Series is now Mohun's unproductive working-class share of total employment over 1964-2010, sourced from mohun_2013_published_shares.csv (Figure 2 (p.10/364)). Benchmark values (table/text-grade): 1964=0.251, 2007=0.300 (share of total employment). SUPERSEDES the fabricated registry formula 'Lu x 0.813'/'Lu x 0.187' (0.813/0.187 are Mohun's working-class/supervisor shares of TOTAL EMPLOYMENT, Section 3, never a split of Lu and never executed). The prior 1948-1989 thousands-FTE series was a mislabeled predecessor-build decomposition (DIV-050), retained as a variant arm (chopped/_variants_predecessor-build/). Annual (non-benchmark) coverage is figure-grade -&gt; deferred to G2 (D4_G2_ACQUISITION_SPEC.md).</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
